--- a/Result/profitability/2377.xlsx
+++ b/Result/profitability/2377.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.58</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7525</v>
+        <v>1.94</v>
       </c>
       <c r="N2" t="n">
-        <v>11.36</v>
+        <v>11.77125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5525</v>
+        <v>1.9275</v>
       </c>
       <c r="N3" t="n">
-        <v>10.88875</v>
+        <v>11.5975</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.96</v>
       </c>
       <c r="M4" t="n">
-        <v>1.60375</v>
+        <v>1.88875</v>
       </c>
       <c r="N4" t="n">
-        <v>11.245</v>
+        <v>11.9575</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>1.48125</v>
+        <v>1.72625</v>
       </c>
       <c r="N5" t="n">
-        <v>11.3825</v>
+        <v>11.99</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>1.215</v>
+        <v>1.4075</v>
       </c>
       <c r="N6" t="n">
-        <v>10.96875</v>
+        <v>11.5575</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9937499999999999</v>
+        <v>1.19625</v>
       </c>
       <c r="N7" t="n">
-        <v>10.83625</v>
+        <v>11.44375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.79875</v>
+        <v>0.7374999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>11.125</v>
+        <v>11.24625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>49913</v>
+      </c>
+      <c r="D75" t="n">
+        <v>41944</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7969</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3281</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.57%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>352</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3633</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2999</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.12375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.2125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.4900000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1212871287128713</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9700000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06466666666666665</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.232704402515723</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.860000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4374437443744377</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
